--- a/real_estate_forms/020_resident_application_form--real_estate_forms.xlsx
+++ b/real_estate_forms/020_resident_application_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_7.1,_'label':_'state_1',_'value':_'state_1'}</t>
+          <t>state_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 7.1, 'label': 'State 1', 'value': 'State 1'}</t>
+          <t>State 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_7.2,_'label':_'state_2',_'value':_'state_2'}</t>
+          <t>state_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 7.2, 'label': 'State 2', 'value': 'State 2'}</t>
+          <t>State 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_7.3,_'label':_'state_3',_'value':_'state_3'}</t>
+          <t>state_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 7.3, 'label': 'State 3', 'value': 'State 3'}</t>
+          <t>State 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_7.4,_'label':_'state_4',_'value':_'state_4'}</t>
+          <t>state_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 7.4, 'label': 'State 4', 'value': 'State 4'}</t>
+          <t>State 4</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_13.1,_'label':_'bi-weekly',_'value':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 13.1, 'label': 'Bi-Weekly', 'value': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_13.2,_'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 13.2, 'label': 'Monthly', 'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_13.3,_'label':_'quarterly',_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 13.3, 'label': 'Quarterly', 'value': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_13.4,_'label':_'annually',_'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 13.4, 'label': 'Annually', 'value': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_17.1,_'label':_'single',_'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 17.1, 'label': 'Single', 'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_17.2,_'label':_'double',_'value':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 17.2, 'label': 'Double', 'value': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_17.3,_'label':_'triple',_'value':_'triple'}</t>
+          <t>triple</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 17.3, 'label': 'Triple', 'value': 'Triple'}</t>
+          <t>Triple</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_17.4,_'label':_'fourplex',_'value':_'fourplex'}</t>
+          <t>fourplex</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 17.4, 'label': 'Fourplex', 'value': 'Fourplex'}</t>
+          <t>Fourplex</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_19.1,_'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 19.1, 'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_19.2,_'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 19.2, 'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_21.1,_'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 21.1, 'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_21.2,_'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 21.2, 'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_22.1,_'label':_'paid',_'value':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 22.1, 'label': 'Paid', 'value': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_22.2,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 22.2, 'label': 'Pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_22.3,_'label':_'not_paid',_'value':_'not_paid'}</t>
+          <t>not_paid</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 22.3, 'label': 'Not Paid', 'value': 'Not Paid'}</t>
+          <t>Not Paid</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_23.1,_'label':_'leased',_'value':_'leased'}</t>
+          <t>leased</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 23.1, 'label': 'Leased', 'value': 'Leased'}</t>
+          <t>Leased</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_23.2,_'label':_'month-to-month',_'value':_'month-to-month'}</t>
+          <t>month-to-month</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 23.2, 'label': 'Month-to-Month', 'value': 'Month-to-Month'}</t>
+          <t>Month-to-Month</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_23.3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 23.3, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_24.1,_'label':_'individual',_'value':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 24.1, 'label': 'Individual', 'value': 'Individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_24.2,_'label':_'couple',_'value':_'couple'}</t>
+          <t>couple</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 24.2, 'label': 'Couple', 'value': 'Couple'}</t>
+          <t>Couple</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_24.3,_'label':_'family',_'value':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 24.3, 'label': 'Family', 'value': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
